--- a/artfynd/A 52726-2025 artfynd.xlsx
+++ b/artfynd/A 52726-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129620772</v>
       </c>
       <c r="B2" t="n">
-        <v>96169</v>
+        <v>96198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129620745</v>
       </c>
       <c r="B3" t="n">
-        <v>56917</v>
+        <v>56920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52726-2025 artfynd.xlsx
+++ b/artfynd/A 52726-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129620772</v>
       </c>
       <c r="B2" t="n">
-        <v>96198</v>
+        <v>96210</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129620745</v>
       </c>
       <c r="B3" t="n">
-        <v>56920</v>
+        <v>56925</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52726-2025 artfynd.xlsx
+++ b/artfynd/A 52726-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129620772</v>
       </c>
       <c r="B2" t="n">
-        <v>96210</v>
+        <v>96211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129620745</v>
       </c>
       <c r="B3" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52726-2025 artfynd.xlsx
+++ b/artfynd/A 52726-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129620772</v>
       </c>
       <c r="B2" t="n">
-        <v>96211</v>
+        <v>96216</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52726-2025 artfynd.xlsx
+++ b/artfynd/A 52726-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129620772</v>
       </c>
       <c r="B2" t="n">
-        <v>96216</v>
+        <v>96220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52726-2025 artfynd.xlsx
+++ b/artfynd/A 52726-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129620772</v>
       </c>
       <c r="B2" t="n">
-        <v>96220</v>
+        <v>96222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52726-2025 artfynd.xlsx
+++ b/artfynd/A 52726-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129620772</v>
       </c>
       <c r="B2" t="n">
-        <v>96222</v>
+        <v>96232</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52726-2025 artfynd.xlsx
+++ b/artfynd/A 52726-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129620772</v>
       </c>
       <c r="B2" t="n">
-        <v>96232</v>
+        <v>96236</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129620745</v>
       </c>
       <c r="B3" t="n">
-        <v>56926</v>
+        <v>56927</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52726-2025 artfynd.xlsx
+++ b/artfynd/A 52726-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129620772</v>
       </c>
       <c r="B2" t="n">
-        <v>96236</v>
+        <v>96239</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129620745</v>
       </c>
       <c r="B3" t="n">
-        <v>56927</v>
+        <v>56930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
